--- a/product_selector_out/STM32U599-5A9.xlsx
+++ b/product_selector_out/STM32U599-5A9.xlsx
@@ -1968,7 +1968,7 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5422,9 +5422,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY12" s="9" t="inlineStr">
@@ -5749,9 +5749,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY13" s="9" t="inlineStr">
@@ -5851,9 +5851,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -5916,14 +5916,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T14" s="6" t="inlineStr">
@@ -6071,19 +6071,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ14" s="6" t="inlineStr">
@@ -6151,9 +6151,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -6403,9 +6403,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY15" s="9" t="inlineStr">
@@ -6730,9 +6730,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY16" s="9" t="inlineStr">
@@ -6832,9 +6832,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -6897,14 +6897,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R17" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S17" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T17" s="6" t="inlineStr">
@@ -7052,19 +7052,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW17" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY17" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ17" s="6" t="inlineStr">
@@ -7132,9 +7132,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -7159,9 +7159,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -7224,14 +7224,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R18" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S18" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T18" s="6" t="inlineStr">
@@ -7379,19 +7379,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW18" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY18" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ18" s="6" t="inlineStr">
@@ -7459,9 +7459,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -7711,9 +7711,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY19" s="9" t="inlineStr">
@@ -8038,9 +8038,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY20" s="9" t="inlineStr">
@@ -8365,9 +8365,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY21" s="9" t="inlineStr">
@@ -8467,9 +8467,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -8532,14 +8532,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R22" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S22" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T22" s="6" t="inlineStr">
@@ -8687,19 +8687,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW22" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY22" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ22" s="6" t="inlineStr">
@@ -8767,9 +8767,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8788,7 +8788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8881,7 +8881,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -8893,7 +8893,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -8903,19 +8903,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STM32U599VJ</t>
+          <t>STM32U599NI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -8925,7 +8925,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
@@ -8937,7 +8937,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -8959,7 +8959,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -8969,7 +8969,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -8991,19 +8991,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM32U5A9VJ</t>
+          <t>STM32U599VJ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -9013,19 +9013,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32U5A9VJ</t>
+          <t>STM32U599VJ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -9035,19 +9035,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STM32U5A9VJ</t>
+          <t>STM32U599ZI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -9057,19 +9057,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32U5A9VJ</t>
+          <t>STM32U599ZI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -9079,7 +9079,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Table 65. Typical dynamic current consumption of peripherals</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
@@ -9091,7 +9091,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -9101,7 +9101,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -9113,7 +9113,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
@@ -9135,7 +9135,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -9145,19 +9145,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32U599ZI</t>
+          <t>STM32U599VI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -9233,7 +9233,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
@@ -9262,7 +9262,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32U5A9NJ</t>
+          <t>STM32U599NJ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9277,14 +9277,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32U5A9NJ</t>
+          <t>STM32U599NJ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9299,14 +9299,14 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32U5A9NJ</t>
+          <t>STM32U599NJ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -9321,19 +9321,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32U5A9NJ</t>
+          <t>STM32U599NJ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -9343,19 +9343,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Table 65. Typical dynamic current consumption of peripherals</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32U5A9BJ</t>
+          <t>STM32U599NJ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -9365,19 +9365,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32U5A9BJ</t>
+          <t>STM32U599BJ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -9387,19 +9387,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32U5A9BJ</t>
+          <t>STM32U599BJ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -9409,19 +9409,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32U5A9BJ</t>
+          <t>STM32U599BJ</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -9431,19 +9431,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Table 65. Typical dynamic current consumption of peripherals</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32U599NJ</t>
+          <t>STM32U599BJ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -9453,19 +9453,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32U599NJ</t>
+          <t>STM32U599BJ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -9475,19 +9475,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32U599NJ</t>
+          <t>STM32U599ZJ</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -9497,19 +9497,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32U599NJ</t>
+          <t>STM32U599ZJ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -9519,19 +9519,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32U599BJ</t>
+          <t>STM32U599ZJ</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -9541,19 +9541,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32U599BJ</t>
+          <t>STM32U599ZJ</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -9563,19 +9563,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32U599BJ</t>
+          <t>STM32U599ZJ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -9585,205 +9585,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>STM32U599BJ</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
           <t>Table 64. Typical dynamic current consumption of peripherals</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>STM32U599ZJ</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>STM32U599ZJ</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>STM32U599ZJ</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>STM32U599ZJ</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>STM32U5A9ZJ</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>STM32U5A9ZJ</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>STM32U5A9ZJ</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>STM32U5A9ZJ</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Table 65. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32U599-5A9.xlsx
+++ b/product_selector_out/STM32U599-5A9.xlsx
@@ -1968,7 +1968,7 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
         </is>
       </c>
     </row>
@@ -5851,9 +5851,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -5916,14 +5916,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T14" s="6" t="inlineStr">
@@ -6071,19 +6071,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ14" s="6" t="inlineStr">
@@ -6151,9 +6151,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -6832,9 +6832,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -6897,14 +6897,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T17" s="6" t="inlineStr">
@@ -7052,19 +7052,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ17" s="6" t="inlineStr">
@@ -7132,9 +7132,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -7159,9 +7159,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -7224,14 +7224,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T18" s="6" t="inlineStr">
@@ -7379,19 +7379,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ18" s="6" t="inlineStr">
@@ -7459,9 +7459,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -8467,9 +8467,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -8532,14 +8532,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T22" s="6" t="inlineStr">
@@ -8687,19 +8687,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ22" s="6" t="inlineStr">
@@ -8767,9 +8767,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -8788,7 +8788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9042,7 +9042,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STM32U599ZI</t>
+          <t>STM32U5A9VJ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -9057,14 +9057,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32U599ZI</t>
+          <t>STM32U5A9VJ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -9079,14 +9079,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32U599ZI</t>
+          <t>STM32U5A9VJ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -9101,14 +9101,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32U599ZI</t>
+          <t>STM32U5A9VJ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -9123,14 +9123,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32U599ZI</t>
+          <t>STM32U5A9VJ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -9145,14 +9145,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+          <t>Table 65. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32U599VI</t>
+          <t>STM32U599ZI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -9174,7 +9174,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32U599VI</t>
+          <t>STM32U599ZI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -9196,7 +9196,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32U599VI</t>
+          <t>STM32U599ZI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -9218,7 +9218,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32U599VI</t>
+          <t>STM32U599ZI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -9240,7 +9240,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32U599VI</t>
+          <t>STM32U599ZI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9262,7 +9262,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32U599NJ</t>
+          <t>STM32U599VI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9284,7 +9284,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32U599NJ</t>
+          <t>STM32U599VI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9306,7 +9306,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32U599NJ</t>
+          <t>STM32U599VI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -9328,7 +9328,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32U599NJ</t>
+          <t>STM32U599VI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -9350,7 +9350,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32U599NJ</t>
+          <t>STM32U599VI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -9372,7 +9372,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32U599BJ</t>
+          <t>STM32U5A9NJ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -9387,14 +9387,14 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32U599BJ</t>
+          <t>STM32U5A9NJ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -9409,14 +9409,14 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32U599BJ</t>
+          <t>STM32U5A9NJ</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -9431,14 +9431,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32U599BJ</t>
+          <t>STM32U5A9NJ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -9453,14 +9453,14 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32U599BJ</t>
+          <t>STM32U5A9NJ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -9475,14 +9475,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+          <t>Table 65. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32U599ZJ</t>
+          <t>STM32U5A9BJ</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -9497,14 +9497,14 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32U599ZJ</t>
+          <t>STM32U5A9BJ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -9519,14 +9519,14 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32U599ZJ</t>
+          <t>STM32U5A9BJ</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -9541,14 +9541,14 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32U599ZJ</t>
+          <t>STM32U5A9BJ</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -9563,29 +9563,469 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>STM32U5A9BJ</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Table 65. Typical dynamic current consumption of peripherals</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>STM32U599NJ</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>STM32U599NJ</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>STM32U599NJ</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>STM32U599NJ</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>STM32U599NJ</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>STM32U599BJ</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>STM32U599BJ</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>STM32U599BJ</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>STM32U599BJ</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>STM32U599BJ</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>STM32U599ZJ</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>STM32U599ZJ</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>STM32U599ZJ</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>STM32U599ZJ</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>STM32U599ZJ</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
         <is>
           <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
         <is>
           <t>Table 64. Typical dynamic current consumption of peripherals</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>STM32U5A9ZJ</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>STM32U5A9ZJ</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>STM32U5A9ZJ</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>STM32U5A9ZJ</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>STM32U5A9ZJ</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Table 65. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32U599-5A9.xlsx
+++ b/product_selector_out/STM32U599-5A9.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM22"/>
+  <dimension ref="A1:BN22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.34375" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -895,6 +896,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -990,6 +996,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1314,6 +1321,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u595ai.pdf</t>
         </is>
       </c>
@@ -1641,6 +1653,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u595ai.pdf</t>
         </is>
       </c>
@@ -1968,6 +1985,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
         </is>
       </c>
@@ -2295,6 +2317,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u595ai.pdf</t>
         </is>
       </c>
@@ -2622,6 +2649,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u595ai.pdf</t>
         </is>
       </c>
@@ -2949,6 +2981,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
         </is>
       </c>
@@ -3276,6 +3313,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
         </is>
       </c>
@@ -3603,6 +3645,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u595ai.pdf</t>
         </is>
       </c>
@@ -3930,6 +3977,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u595ai.pdf</t>
         </is>
       </c>
@@ -4257,6 +4309,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u595ai.pdf</t>
         </is>
       </c>
@@ -4584,12 +4641,17 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -4610,16 +4672,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -4632,6 +4692,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -4651,7 +4712,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -4679,7 +4742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM22"/>
+  <dimension ref="A1:BN22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4747,6 +4810,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5080,6 +5144,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -5175,6 +5244,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -5497,7 +5567,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5824,7 +5899,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6151,7 +6231,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6478,7 +6563,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6805,7 +6895,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7132,7 +7227,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7459,7 +7559,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7786,7 +7891,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8113,7 +8223,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8440,7 +8555,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8767,7 +8887,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8775,8 +8900,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
